--- a/data/trans_orig/IP2907_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18244</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>41911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>49708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39504</t>
+          <t>40597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84940</t>
+          <t>85059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98733</t>
+          <t>98448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74100</t>
+          <t>74537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102573</t>
+          <t>102534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123013</t>
+          <t>120643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163103</t>
+          <t>161532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211906</t>
+          <t>210501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>317345</t>
+          <t>317384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345818</t>
+          <t>345381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377891</t>
+          <t>380261</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>419880</t>
+          <t>421295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708915</t>
+          <t>710320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>757718</t>
+          <t>759289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>27046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46389</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48935</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72185</t>
+          <t>73264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110659</t>
+          <t>111774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125666</t>
+          <t>126177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132240</t>
+          <t>131774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151366</t>
+          <t>151583</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>249250</t>
+          <t>248171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272500</t>
+          <t>273082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100839</t>
+          <t>100375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134116</t>
+          <t>135129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125043</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172695</t>
+          <t>171111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236734</t>
+          <t>236704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>295564</t>
+          <t>293704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>481476</t>
+          <t>480463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514753</t>
+          <t>515217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>564585</t>
+          <t>566169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612237</t>
+          <t>610710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1057308</t>
+          <t>1059168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1116138</t>
+          <t>1116168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP2907_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10755</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16647</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6475</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3160</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10957</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10355</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>22,99%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>16956</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>11681</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,23%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>18155</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>12167</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42365</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36473</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>46815</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>46393</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41911</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49708</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46067</t>
+          <t>38834</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40597</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50847</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>92460</t>
+          <t>81199</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85059</t>
+          <t>74649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98448</t>
+          <t>86474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53120</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53120</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53120</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>52868</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>52868</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52868</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57748</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57748</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57748</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>110615</t>
+          <t>98155</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>110615</t>
+          <t>98155</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110615</t>
+          <t>98155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86574</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71632</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>105204</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>87674</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>74537</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>102534</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79609</t>
+          <t>74785</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>103483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>185903</t>
+          <t>174094</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161532</t>
+          <t>153128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210501</t>
+          <t>197301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>375621</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>356991</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>390563</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>487</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>332244</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>317384</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>345381</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>402674</t>
+          <t>328488</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>380261</t>
+          <t>312525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>421295</t>
+          <t>341223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>734918</t>
+          <t>704108</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710320</t>
+          <t>680901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>759289</t>
+          <t>725074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>462195</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>462195</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>462195</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>419918</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>419918</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>419918</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>500904</t>
+          <t>416008</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>500904</t>
+          <t>416008</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>500904</t>
+          <t>416008</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>920821</t>
+          <t>878202</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>920821</t>
+          <t>878202</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>920821</t>
+          <t>878202</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33420</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25279</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42751</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>23277</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16630</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31033</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35997</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27046</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46855</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59274</t>
+          <t>55904</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48353</t>
+          <t>44596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73264</t>
+          <t>67814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130846</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121515</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138987</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>119530</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>111774</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126177</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>83,7%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>142632</t>
+          <t>121077</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>113853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151583</t>
+          <t>127165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>262161</t>
+          <t>251923</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248171</t>
+          <t>240013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273082</t>
+          <t>263231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>142807</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>142807</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>142807</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178629</t>
+          <t>143561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>307827</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>307827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>307827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>130749</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>111678</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150256</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>117425</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>100375</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>135129</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>19,08%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116204</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126570</t>
+          <t>100342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171111</t>
+          <t>134235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246953</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236704</t>
+          <t>221356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293704</t>
+          <t>272415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>548832</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>529325</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>567903</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>498167</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>480463</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>515217</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>80,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>591373</t>
+          <t>488399</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>566169</t>
+          <t>470368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610710</t>
+          <t>504261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1089540</t>
+          <t>1037231</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1059168</t>
+          <t>1011769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1116168</t>
+          <t>1062828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,76%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>903</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>615592</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>615592</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>615592</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>604603</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>604603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>604603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1352872</t>
+          <t>1284184</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1352872</t>
+          <t>1284184</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1352872</t>
+          <t>1284184</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
